--- a/data/network_500kv/buses_PSSE_vs_geosadi.xlsx
+++ b/data/network_500kv/buses_PSSE_vs_geosadi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\pypsa-ar-base\data\network_500kv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89EF16C-B570-4414-8730-F1464458751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DBB491-16F3-4429-957F-0151B034CD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B6A7DE32-F623-4F3B-A33D-1C155ACFA8CC}"/>
   </bookViews>
@@ -2760,10 +2760,10 @@
         <v>67</v>
       </c>
       <c r="D48">
-        <v>-34.752712000000002</v>
+        <v>-34.9118465411849</v>
       </c>
       <c r="E48">
-        <v>-58.542000000000002</v>
+        <v>-58.724642214966202</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>170</v>

--- a/data/network_500kv/buses_PSSE_vs_geosadi.xlsx
+++ b/data/network_500kv/buses_PSSE_vs_geosadi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\pypsa-ar-base\data\network_500kv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DBB491-16F3-4429-957F-0151B034CD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5022B5DA-DD3B-4D33-828C-DF0FF9DB152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B6A7DE32-F623-4F3B-A33D-1C155ACFA8CC}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="188">
   <si>
     <t>bus_id</t>
   </si>
@@ -470,9 +470,6 @@
     <t>zone</t>
   </si>
   <si>
-    <t>VERIFICADO?</t>
-  </si>
-  <si>
     <t xml:space="preserve">B.AIRES     </t>
   </si>
   <si>
@@ -575,9 +572,6 @@
     <t xml:space="preserve">PATAGONI    </t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAN JUAN    </t>
   </si>
   <si>
@@ -593,498 +587,30 @@
     <t>CERRITO DE LA COSTA</t>
   </si>
   <si>
-    <t>Compensador serie en el extremo Río Diamante de la línea Agua de Cajón–Río Diamante</t>
-  </si>
-  <si>
     <t>RINCON STA. MARIA</t>
   </si>
   <si>
-    <r>
-      <t>6006 MALVINAS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 258.5 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8004 REC.MALV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → compensador serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8002 RECREO. No existe en GEOSADI COORD MANUALES</t>
-    </r>
-  </si>
-  <si>
-    <t>2008 OLAVARRI → comp. serie (len=0) → 2012 OLA.AB1 → línea real 291.0 km → 3002 ABASTO. Compensador en serie. No existe en GEOSADI COORD MANUALES</t>
-  </si>
-  <si>
-    <t>2008 OLAVARRI → comp. serie (len=0) → 2013 OLA.AB2 → línea real 301.9 km → 3002 ABASTO.  Compensador en serie. No existe en GEOSADI COORD MANUALES</t>
-  </si>
-  <si>
-    <t>1014 T.AGUI1 (Piedra del Águila) → línea real 386.7 km → 1007 CHOE.PA → comp. serie (r=0, x&lt;0, len=0) → 1008 CH.CHOEL.  Compensador en serie. No existe en GEOSADI COORD MANUALES</t>
-  </si>
-  <si>
-    <r>
-      <t>2000 B.BLANCA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 408.4 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2049 VIVO.BB1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2050 VIVORATA.   Compensador en serie. No existe en GEOSADI</t>
-    </r>
-  </si>
-  <si>
-    <t>Bus 1002 P.AGUILA solo conecta con 1014 (×2, 5.9 km) → es la Casa de Máquinas → P. DEL AGUILA (CH)</t>
-  </si>
-  <si>
     <t>P. DEL AGUILA (CH)</t>
   </si>
   <si>
     <t>P. DEL AGUILA</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Bus 1014 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>T.AGUI1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tiene todas las conexiones largas hacia Choele Choel, Chocón Oeste, Alicura, PP Leufú → es la </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ET</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>P. DEL AGUILA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1008 CH.CHOEL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>1010 CHOE.BB1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 346.0 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2000 B.BLANCA. Compensador en serie. No existe en GEOSADI</t>
-    </r>
-  </si>
-  <si>
-    <t>1008 CH.CHOEL → comp. serie (r=0, x&lt;0, len=0) → 1011 CHOE.BB2 → línea real 348.4 km → 2000 B.BLANCA. Compensador en serie. No existe en GEOSADI</t>
-  </si>
-  <si>
-    <r>
-      <t>7000 GRAN MZA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 188.1 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>7005 RDIAM.GM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x=-0.01301, len=0.05 km) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>7002 RDIAMANT.Compensador en serie. No existe en GEOSADI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5016 CHACO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 264.0 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8011 MQUEM-CH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t xml:space="preserve">8010 MQUEMADO. Compensador en serie. No existe en GEOSADI </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>8007 COBOS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 297.7 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8009 MQUEM-CB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8010 MQUEMADO. Compensador en serie. No existe en GEOSADI</t>
-    </r>
-  </si>
-  <si>
     <t>CENTRAL GENELBA</t>
   </si>
   <si>
-    <t xml:space="preserve">10 NPMADRYN → comp. serie (r=0, x&lt;0, len=0) → 11 NPMD.CHL → línea real 354.0 km → 1008 CH.CHOEL. Compensador en serie. No existe en GEOSADI </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Está a 0.5 km de Bahía Blanca y conecta hacia Piedra Buena a 27 km. No tiene generadores ni cargas en el .raw. No tiene más conexiones que esas dos ramas </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Podria ser PE PAMPA VI de geosad pero que en este snapshot no estaba generando?  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(no la encuentro en psse esta estacion sino)</t>
-    </r>
-  </si>
-  <si>
-    <t>2008 OLAVARRI → comp. serie (r=0, x&lt;0, len=0) → 2010 OLA.BB1 → línea real 255.0 km → 2000 B.BLANCA</t>
-  </si>
-  <si>
-    <r>
-      <t>2008 OLAVARRI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → comp. serie (r=0, x&lt;0, len=0) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2011 OLA.BB2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 254.8 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>2000 B.BLANCA</t>
-    </r>
-  </si>
-  <si>
-    <t>CONSULTAR</t>
-  </si>
-  <si>
-    <t>No aparece en GEOSADI porque es la central generadora TERMINAL 6, no una estacion electrica. Luego conecta a la red de 500 con una linea de 12,4 hacia bus 4019 (CN-TSE). Esta linea si esta en GEOSADI pero los extremos no estaban bien definidos, extraere su geometria para matchear la linea manualmente</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Topologia. 5004 RESISTEN → switching device → 5013 R9B5RS → shunt 100 MVAR. Aparece en SWITCHED SHUNT DATA con 100 MVAR — tiene un banco de compensación reactiva (capacitor o reactor). No tiene ramas normales, ni loads, ni generacion ni transformadores. Lo mantenemos como BUS? Si es asi asignar mismos coord q bus 5004</t>
-  </si>
-  <si>
-    <t>10 NPMADRYN → línea real 552.3 km → 12 SCN_500 → línea real 391.9 km → 15 RSCRUZ</t>
-  </si>
-  <si>
     <t>SANTA CRUZ NORTE</t>
   </si>
   <si>
-    <r>
-      <t>5004 RESISTEN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → switching device → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>5012 R6L5RS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → línea real 42 km → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>5005 P.PATRIA. Esta necesita existir ya que es el unico camino para conectar RESISTENCIA y PASO LA PATRIA. En PyPSA deberemos crear la linea 5004 RESISTEN → 5012 R6L5RS con los parámetros del switching device (r=1e-4, x=0, len≈0) — representa la conexión interna dentro de Resistencia</t>
-    </r>
-  </si>
-  <si>
-    <t>Unidad generadora de casa de maquinas de Salto Grande, GEOSADI no tiene como estacion pero si existe linea que la conecta</t>
-  </si>
-  <si>
     <t>EL CHOCON (CH)</t>
-  </si>
-  <si>
-    <t>Conecta a 1000 CHOCON via 3x lineas de 1,3km coincide con la sala de maquinas</t>
-  </si>
-  <si>
-    <t>Nodo de conexión de TERMINAL 6 con red de 500, cercano a Rio corondo. GEOSADI tenia la linea pero los cabezales no estaban definidos</t>
-  </si>
-  <si>
-    <t>geosadi_line_id</t>
-  </si>
-  <si>
-    <t>Notas</t>
-  </si>
-  <si>
-    <t>Estacion electrica bypass de EZEIZA no existe en GEOSADI.. ABASTO —58km— EZEIZA —54/60km— RODRIGUEZ ; ABASTO —58km— EZBPASS —60km—   RODRIGUEZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1105,11 +631,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1132,12 +653,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1475,17 +994,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DD5816-A543-4D91-B4ED-BEC07CE463BC}">
-  <dimension ref="A1:U102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:R102"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.90625" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" customWidth="1"/>
-    <col min="21" max="21" width="33.1796875" customWidth="1"/>
+    <col min="18" max="18" width="33.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1507,17 +1024,8 @@
       <c r="G1" t="s">
         <v>142</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1533,17 +1041,14 @@
       <c r="E2">
         <v>-65.105115802652094</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="F2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>11</v>
       </c>
@@ -1556,23 +1061,14 @@
       <c r="E3">
         <v>-65.106295000000003</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I3">
-        <v>1832</v>
-      </c>
-      <c r="J3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="F3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>12</v>
       </c>
@@ -1580,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="D4">
         <v>-46.774281502789101</v>
@@ -1588,20 +1084,14 @@
       <c r="E4">
         <v>-67.979200139574701</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H4" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="F4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>15</v>
       </c>
@@ -1609,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D5">
         <v>-49.986180910220803</v>
@@ -1617,17 +1107,14 @@
       <c r="E5">
         <v>-68.973397016559005</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="F5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>19</v>
       </c>
@@ -1643,17 +1130,14 @@
       <c r="E6">
         <v>-70.714270464510307</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="F6" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -1669,17 +1153,14 @@
       <c r="E7">
         <v>-68.748146024319496</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="F7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1002</v>
       </c>
@@ -1687,7 +1168,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D8">
         <v>-40.189261874935497</v>
@@ -1695,20 +1176,14 @@
       <c r="E8">
         <v>-69.991493972268998</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" t="s">
-        <v>178</v>
-      </c>
-      <c r="J8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="F8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1004</v>
       </c>
@@ -1716,7 +1191,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D9">
         <v>-39.2373797693608</v>
@@ -1724,17 +1199,14 @@
       <c r="E9">
         <v>-68.779399257769498</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="F9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1006</v>
       </c>
@@ -1750,17 +1222,14 @@
       <c r="E10">
         <v>-65.691999487985896</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="F10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1007</v>
       </c>
@@ -1773,23 +1242,14 @@
       <c r="E11">
         <v>-65.694339999999997</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H11" t="s">
-        <v>178</v>
-      </c>
-      <c r="I11">
-        <v>56</v>
-      </c>
-      <c r="J11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="F11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1008</v>
       </c>
@@ -1805,17 +1265,14 @@
       <c r="E12">
         <v>-65.691899487985793</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="F12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1010</v>
       </c>
@@ -1828,23 +1285,14 @@
       <c r="E13">
         <v>-62.054946999999999</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" t="s">
-        <v>178</v>
-      </c>
-      <c r="I13">
-        <v>73</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="F13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1011</v>
       </c>
@@ -1857,23 +1305,14 @@
       <c r="E14">
         <v>-62.054946999999999</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I14">
-        <v>2747</v>
-      </c>
-      <c r="J14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="F14" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1012</v>
       </c>
@@ -1881,7 +1320,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D15">
         <v>-38.7197148748415</v>
@@ -1889,17 +1328,14 @@
       <c r="E15">
         <v>-68.257366844404302</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H15" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="F15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1014</v>
       </c>
@@ -1907,7 +1343,7 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D16">
         <v>-40.162892630190697</v>
@@ -1915,20 +1351,14 @@
       <c r="E16">
         <v>-70.044752489335806</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" t="s">
-        <v>178</v>
-      </c>
-      <c r="J16" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="F16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1016</v>
       </c>
@@ -1944,17 +1374,14 @@
       <c r="E17">
         <v>-70.748659606955201</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H17" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="F17" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1018</v>
       </c>
@@ -1962,7 +1389,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D18">
         <v>-39.265852183031797</v>
@@ -1970,20 +1397,14 @@
       <c r="E18">
         <v>-68.756690670138298</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" t="s">
-        <v>178</v>
-      </c>
-      <c r="J18" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="F18" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1020</v>
       </c>
@@ -1999,17 +1420,14 @@
       <c r="E19">
         <v>-68.604384133321005</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="F19" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1022</v>
       </c>
@@ -2025,17 +1443,14 @@
       <c r="E20">
         <v>-69.984383930374094</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="F20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1024</v>
       </c>
@@ -2051,17 +1466,14 @@
       <c r="E21">
         <v>-68.472922671943707</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="F21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1025</v>
       </c>
@@ -2077,17 +1489,14 @@
       <c r="E22">
         <v>-68.355984070908093</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="F22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1026</v>
       </c>
@@ -2103,17 +1512,14 @@
       <c r="E23">
         <v>-65.822959635778503</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="F23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1028</v>
       </c>
@@ -2129,17 +1535,14 @@
       <c r="E24">
         <v>-65.822859635778499</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="F24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1030</v>
       </c>
@@ -2155,17 +1558,14 @@
       <c r="E25">
         <v>-63.564656843738298</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="F25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2000</v>
       </c>
@@ -2181,17 +1581,14 @@
       <c r="E26">
         <v>-62.053766236622501</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H26" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="F26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2001</v>
       </c>
@@ -2207,17 +1604,14 @@
       <c r="E27">
         <v>-62.415758265531501</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="F27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2002</v>
       </c>
@@ -2233,17 +1627,14 @@
       <c r="E28">
         <v>-58.998793474739003</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H28" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="F28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -2259,24 +1650,21 @@
       <c r="E29">
         <v>-59.003399444328899</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="F29" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2004</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D30">
@@ -2285,17 +1673,14 @@
       <c r="E30">
         <v>-61.670735063072598</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="F30" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2005</v>
       </c>
@@ -2308,20 +1693,14 @@
       <c r="E31">
         <v>-62.046672000000001</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" t="s">
-        <v>205</v>
-      </c>
-      <c r="J31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="F31" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2006</v>
       </c>
@@ -2337,17 +1716,14 @@
       <c r="E32">
         <v>-61.670635063072503</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="F32" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2008</v>
       </c>
@@ -2363,17 +1739,14 @@
       <c r="E33">
         <v>-60.343998589962901</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="F33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2010</v>
       </c>
@@ -2386,23 +1759,14 @@
       <c r="E34">
         <v>-60.347101000000002</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H34" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34">
-        <v>75</v>
-      </c>
-      <c r="J34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="F34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2011</v>
       </c>
@@ -2415,23 +1779,14 @@
       <c r="E35">
         <v>-60.388827999999997</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H35" t="s">
-        <v>178</v>
-      </c>
-      <c r="I35">
-        <v>76</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="F35" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2012</v>
       </c>
@@ -2444,23 +1799,14 @@
       <c r="E36">
         <v>-58.161076999999999</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H36" t="s">
-        <v>178</v>
-      </c>
-      <c r="I36">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="F36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2013</v>
       </c>
@@ -2473,23 +1819,14 @@
       <c r="E37">
         <v>-58.159911999999998</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H37" t="s">
-        <v>178</v>
-      </c>
-      <c r="I37">
-        <v>78</v>
-      </c>
-      <c r="J37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="F37" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2014</v>
       </c>
@@ -2497,7 +1834,7 @@
         <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D38">
         <v>-38.786596793507201</v>
@@ -2505,17 +1842,14 @@
       <c r="E38">
         <v>-62.251757217321597</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="F38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2016</v>
       </c>
@@ -2523,7 +1857,7 @@
         <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D39">
         <v>-38.786596793507201</v>
@@ -2531,17 +1865,14 @@
       <c r="E39">
         <v>-62.251757217321597</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H39" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="F39" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2018</v>
       </c>
@@ -2557,17 +1888,14 @@
       <c r="E40">
         <v>-59.204788887497102</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="F40" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2020</v>
       </c>
@@ -2583,17 +1911,14 @@
       <c r="E41">
         <v>-60.0694998357488</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H41" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="F41" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2049</v>
       </c>
@@ -2606,23 +1931,14 @@
       <c r="E42">
         <v>-57.731158999999998</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H42" t="s">
-        <v>178</v>
-      </c>
-      <c r="I42">
-        <v>2629</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="F42" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2050</v>
       </c>
@@ -2638,17 +1954,14 @@
       <c r="E43">
         <v>-57.731856250165798</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H43" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="F43" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2090</v>
       </c>
@@ -2664,17 +1977,14 @@
       <c r="E44">
         <v>-60.180114683845503</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H44" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="F44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2092</v>
       </c>
@@ -2690,17 +2000,14 @@
       <c r="E45">
         <v>-60.169664508610097</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H45" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="F45" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>3000</v>
       </c>
@@ -2716,17 +2023,14 @@
       <c r="E46">
         <v>-58.724642214966202</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H46" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+      <c r="F46" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>3002</v>
       </c>
@@ -2742,17 +2046,14 @@
       <c r="E47">
         <v>-58.164927322937601</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="F47" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>3003</v>
       </c>
@@ -2765,20 +2066,14 @@
       <c r="E48">
         <v>-58.724642214966202</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H48" t="s">
-        <v>178</v>
-      </c>
-      <c r="J48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="F48" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>3004</v>
       </c>
@@ -2794,17 +2089,14 @@
       <c r="E49">
         <v>-58.9318933708823</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H49" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="F49" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>3005</v>
       </c>
@@ -2812,7 +2104,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D50">
         <v>-34.902737977275798</v>
@@ -2820,17 +2112,14 @@
       <c r="E50">
         <v>-58.732736206910403</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H50" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+      <c r="F50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>3006</v>
       </c>
@@ -2838,7 +2127,7 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D51">
         <v>-34.902737977275798</v>
@@ -2846,17 +2135,14 @@
       <c r="E51">
         <v>-58.732736206910403</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H51" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="F51" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>3007</v>
       </c>
@@ -2864,7 +2150,7 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D52">
         <v>-34.902737977275798</v>
@@ -2872,17 +2158,14 @@
       <c r="E52">
         <v>-58.732736206910403</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H52" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="F52" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>4000</v>
       </c>
@@ -2898,17 +2181,14 @@
       <c r="E53">
         <v>-60.779984896985397</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="F53" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>4002</v>
       </c>
@@ -2924,17 +2204,14 @@
       <c r="E54">
         <v>-60.7936421166903</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H54" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+      <c r="F54" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>4004</v>
       </c>
@@ -2950,17 +2227,14 @@
       <c r="E55">
         <v>-58.293988353479698</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H55" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="F55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>4006</v>
       </c>
@@ -2976,17 +2250,14 @@
       <c r="E56">
         <v>-59.763139807456099</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H56" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+      <c r="F56" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>4008</v>
       </c>
@@ -3002,17 +2273,14 @@
       <c r="E57">
         <v>-57.963520830421899</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H57" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+      <c r="F57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>4009</v>
       </c>
@@ -3028,17 +2296,14 @@
       <c r="E58">
         <v>-60.425569443175199</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H58" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+      <c r="F58" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>4010</v>
       </c>
@@ -3054,17 +2319,14 @@
       <c r="E59">
         <v>-60.8624150416208</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H59" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+      <c r="F59" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>4012</v>
       </c>
@@ -3077,23 +2339,14 @@
       <c r="E60">
         <v>-57.932400000000001</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H60" t="s">
-        <v>178</v>
-      </c>
-      <c r="I60">
-        <v>2871</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="F60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>4013</v>
       </c>
@@ -3106,23 +2359,14 @@
       <c r="E61">
         <v>-57.932299999999998</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H61" t="s">
-        <v>178</v>
-      </c>
-      <c r="I61">
-        <v>2872</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="F61" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>4014</v>
       </c>
@@ -3135,23 +2379,14 @@
       <c r="E62">
         <v>-57.932200000000002</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H62" t="s">
-        <v>178</v>
-      </c>
-      <c r="I62">
-        <v>2873</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="F62" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>4015</v>
       </c>
@@ -3164,23 +2399,14 @@
       <c r="E63">
         <v>-57.932099999999998</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H63" t="s">
-        <v>178</v>
-      </c>
-      <c r="I63">
-        <v>2874</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+      <c r="F63" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4018</v>
       </c>
@@ -3193,23 +2419,14 @@
       <c r="E64">
         <v>-60.750729</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" t="s">
-        <v>178</v>
-      </c>
-      <c r="I64">
-        <v>3250</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21">
+      <c r="F64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4019</v>
       </c>
@@ -3222,23 +2439,14 @@
       <c r="E65">
         <v>-60.819420000000001</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H65" t="s">
-        <v>178</v>
-      </c>
-      <c r="I65">
-        <v>3250</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21">
+      <c r="F65" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>5000</v>
       </c>
@@ -3254,17 +2462,14 @@
       <c r="E66">
         <v>-56.7392780143688</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H66" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21">
+      <c r="F66" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>5002</v>
       </c>
@@ -3272,7 +2477,7 @@
         <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D67">
         <v>-27.488718112650801</v>
@@ -3280,17 +2485,14 @@
       <c r="E67">
         <v>-56.697682987479801</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H67" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21">
+      <c r="F67" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>5004</v>
       </c>
@@ -3306,17 +2508,14 @@
       <c r="E68">
         <v>-59.108568069161002</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H68" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" ht="14.5" customHeight="1">
+      <c r="F68" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>5005</v>
       </c>
@@ -3332,28 +2531,25 @@
       <c r="E69">
         <v>-58.687925029016803</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H69" t="s">
-        <v>178</v>
-      </c>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-      <c r="R69" s="5"/>
-      <c r="S69" s="5"/>
-      <c r="T69" s="5"/>
-      <c r="U69" s="5"/>
-    </row>
-    <row r="70" spans="1:21">
+      <c r="F69" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>5006</v>
       </c>
@@ -3369,17 +2565,14 @@
       <c r="E70">
         <v>-58.248457573158397</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H70" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21">
+      <c r="F70" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>5012</v>
       </c>
@@ -3392,43 +2585,28 @@
       <c r="E71">
         <v>-59.104564000000003</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I71">
-        <v>365</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21">
+      <c r="F71" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>5013</v>
       </c>
       <c r="B72" t="s">
         <v>101</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H72" t="s">
-        <v>205</v>
-      </c>
-      <c r="J72" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21">
+      <c r="F72" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>5016</v>
       </c>
@@ -3444,17 +2622,14 @@
       <c r="E73">
         <v>-60.439342292312901</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H73" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21">
+      <c r="F73" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>5030</v>
       </c>
@@ -3470,17 +2645,14 @@
       <c r="E74">
         <v>-57.7017029442354</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H74" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21">
+      <c r="F74" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>5253</v>
       </c>
@@ -3496,17 +2668,14 @@
       <c r="E75">
         <v>-55.9181895192309</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H75" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21">
+      <c r="F75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>6000</v>
       </c>
@@ -3522,17 +2691,14 @@
       <c r="E76">
         <v>-64.317293633794094</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H76" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21">
+      <c r="F76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>6002</v>
       </c>
@@ -3548,17 +2714,14 @@
       <c r="E77">
         <v>-63.423248501916802</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H77" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21">
+      <c r="F77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>6004</v>
       </c>
@@ -3574,17 +2737,14 @@
       <c r="E78">
         <v>-64.442601984993601</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H78" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21">
+      <c r="F78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>6006</v>
       </c>
@@ -3600,17 +2760,14 @@
       <c r="E79">
         <v>-63.9129519775517</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H79" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21">
+      <c r="F79" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>6008</v>
       </c>
@@ -3626,17 +2783,14 @@
       <c r="E80">
         <v>-64.636454416038404</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H80" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+      <c r="F80" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>6010</v>
       </c>
@@ -3652,17 +2806,14 @@
       <c r="E81">
         <v>-66.065164479956806</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H81" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+      <c r="F81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>7000</v>
       </c>
@@ -3678,17 +2829,14 @@
       <c r="E82">
         <v>-68.581952702355295</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H82" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+      <c r="F82" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>7002</v>
       </c>
@@ -3704,17 +2852,14 @@
       <c r="E83">
         <v>-68.593720591232298</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H83" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+      <c r="F83" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>7003</v>
       </c>
@@ -3727,23 +2872,14 @@
       <c r="E84">
         <v>-68.268417999999997</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H84" t="s">
-        <v>178</v>
-      </c>
-      <c r="I84">
-        <v>2374</v>
-      </c>
-      <c r="J84" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+      <c r="F84" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>7005</v>
       </c>
@@ -3756,23 +2892,14 @@
       <c r="E85">
         <v>-68.595929999999996</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H85" t="s">
-        <v>178</v>
-      </c>
-      <c r="I85">
-        <v>2375</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+      <c r="F85" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>7010</v>
       </c>
@@ -3788,17 +2915,14 @@
       <c r="E86">
         <v>-68.6190063264808</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H86" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+      <c r="F86" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>8000</v>
       </c>
@@ -3814,17 +2938,14 @@
       <c r="E87">
         <v>-65.165523545974807</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H87" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+      <c r="F87" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>8002</v>
       </c>
@@ -3840,17 +2961,14 @@
       <c r="E88">
         <v>-65.057446922837201</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H88" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+      <c r="F88" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>8004</v>
       </c>
@@ -3863,23 +2981,14 @@
       <c r="E89">
         <v>-65.048929999999999</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H89" t="s">
-        <v>178</v>
-      </c>
-      <c r="I89">
-        <v>356</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+      <c r="F89" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>8006</v>
       </c>
@@ -3895,17 +3004,14 @@
       <c r="E90">
         <v>-66.512936117307902</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H90" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+      <c r="F90" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>8007</v>
       </c>
@@ -3921,17 +3027,14 @@
       <c r="E91">
         <v>-65.047180684141196</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H91" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+      <c r="F91" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>8008</v>
       </c>
@@ -3947,17 +3050,14 @@
       <c r="E92">
         <v>-64.997537302304593</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H92" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+      <c r="F92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>8009</v>
       </c>
@@ -3970,23 +3070,14 @@
       <c r="E93">
         <v>-62.817701999999997</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H93" t="s">
-        <v>178</v>
-      </c>
-      <c r="I93">
-        <v>2017</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+      <c r="F93" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>8010</v>
       </c>
@@ -4002,17 +3093,14 @@
       <c r="E94">
         <v>-62.816578063326901</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+      <c r="F94" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>8011</v>
       </c>
@@ -4025,23 +3113,14 @@
       <c r="E95">
         <v>-62.817701999999997</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H95" t="s">
-        <v>178</v>
-      </c>
-      <c r="I95">
-        <v>2016</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+      <c r="F95" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>8012</v>
       </c>
@@ -4057,17 +3136,14 @@
       <c r="E96">
         <v>-65.104461946961194</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H96" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+      <c r="F96" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>8013</v>
       </c>
@@ -4083,22 +3159,19 @@
       <c r="E97">
         <v>-64.346174574396997</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H97" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="D102" s="3"/>
+      <c r="F97" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D102" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H97" xr:uid="{26DD5816-A543-4D91-B4ED-BEC07CE463BC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J104">
+  <autoFilter ref="A1:G97" xr:uid="{26DD5816-A543-4D91-B4ED-BEC07CE463BC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G104">
     <sortCondition ref="A1:A104"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
